--- a/excel_files/3.3.2.xlsx
+++ b/excel_files/3.3.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D109CCBC-E858-4205-B7B4-7EA8691C9869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14175" yWindow="480" windowWidth="14580" windowHeight="12990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -145,7 +146,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -272,104 +273,91 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -385,9 +373,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -425,9 +413,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -462,7 +450,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -497,7 +485,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -670,42 +658,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="34.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="3" width="34.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="7" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -718,1926 +694,2019 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="13">
         <v>2007</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="13">
         <v>2008</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="13">
         <v>2009</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="13">
         <v>2010</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="13">
         <v>2011</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="13">
         <v>2012</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="13">
         <v>2013</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="13">
         <v>2014</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="13">
         <v>2015</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="13">
         <v>2016</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="13">
         <v>2017</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="13">
         <v>2018</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="13">
         <v>2019</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="13">
         <v>2020</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="13">
         <v>2021</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="13">
         <v>2022</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="13">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="U3" s="13">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <v>115.47827556538839</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="24">
         <v>106.34008217309378</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="24">
         <v>103.93297614074103</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="24">
         <v>101.13877488087284</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="24">
         <v>100.36712426338509</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="24">
         <v>104.34219388958846</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="24">
         <v>102.43272028716828</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="24">
         <v>101.06555792711764</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="24">
         <v>98.249685132672326</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="24">
         <v>93.423511145030133</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="25">
         <v>90.6</v>
       </c>
-      <c r="O4" s="21">
+      <c r="O4" s="18">
         <v>83.012882100040883</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="28">
         <v>78.928028510736837</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="28">
         <v>53.463696812512026</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="28">
         <v>58.14349653559799</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="28">
         <v>57.890663775669807</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="28">
         <v>52.734251206028382</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="U4" s="28">
+        <v>49.447040571774508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>91.061331591598659</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>85.809102997291632</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="14">
         <v>85.417203809702642</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="14">
         <v>84.9</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="14">
         <v>81.947250039397716</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="14">
         <v>85.223607996779961</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="14">
         <v>87.8</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="14">
         <v>88.7</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="14">
         <v>83.7</v>
       </c>
-      <c r="M5" s="17">
+      <c r="M5" s="14">
         <v>81.7</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="15">
         <v>77.7</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="19">
         <v>69.021989778470783</v>
       </c>
-      <c r="P5" s="31">
+      <c r="P5" s="26">
         <v>66.863516959508374</v>
       </c>
-      <c r="Q5" s="31">
+      <c r="Q5" s="26">
         <v>46.05204738706685</v>
       </c>
-      <c r="R5" s="31">
+      <c r="R5" s="26">
         <v>50.405857641278807</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="26">
         <v>50.022742766269019</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="26">
         <v>44.646801162600475</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="U5" s="26">
+        <v>44.205393660952026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>140.46198978105025</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="14">
         <v>127.33842276048124</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="14">
         <v>122.93631853530373</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>117.8</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>119.25600705766379</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="14">
         <v>123.92298365249006</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="14">
         <v>117.4</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="14">
         <v>113.7</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="14">
         <v>113.1</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="14">
         <v>105.3</v>
       </c>
-      <c r="N6" s="18">
+      <c r="N6" s="15">
         <v>103.8</v>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="19">
         <v>97.234291910164316</v>
       </c>
-      <c r="P6" s="32">
+      <c r="P6" s="26">
         <v>91.178104768980091</v>
       </c>
-      <c r="Q6" s="32">
+      <c r="Q6" s="26">
         <v>60.76705279190513</v>
       </c>
-      <c r="R6" s="32">
+      <c r="R6" s="26">
         <v>65.995789757646122</v>
       </c>
-      <c r="S6" s="32">
+      <c r="S6" s="26">
         <v>65.935557126462314</v>
       </c>
-      <c r="T6" s="32">
+      <c r="T6" s="26">
         <v>60.998061560200554</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="U6" s="26">
+        <v>54.800010747295261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="11">
         <v>80.315042230167364</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="11">
         <v>81.679898810273926</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <v>82.704723229572977</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="11">
         <v>81.837550176933703</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="11">
         <v>78.88083600202259</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="11">
         <v>90.334236675700083</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="11">
         <v>90.03226515148252</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="11">
         <v>86.073370708958365</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="11">
         <v>72.743562502953921</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="11">
         <v>67.061001417516977</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="12">
         <v>70.8</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="19">
         <v>64.887678850275051</v>
       </c>
-      <c r="P7" s="32">
+      <c r="P7" s="26">
         <v>55.906408530903825</v>
       </c>
-      <c r="Q7" s="32">
+      <c r="Q7" s="26">
         <v>46.609654277955656</v>
       </c>
-      <c r="R7" s="32">
+      <c r="R7" s="26">
         <v>47.339416388110941</v>
       </c>
-      <c r="S7" s="35">
+      <c r="S7" s="28">
         <v>41.756312988336546</v>
       </c>
-      <c r="T7" s="35">
+      <c r="T7" s="28">
         <v>41.931627189714625</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="U7" s="28">
+        <v>37.009559671124222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="11">
         <v>70.83724905904522</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="11">
         <v>67.323066565682069</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>81.332337169823802</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="11">
         <v>62.3</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="11">
         <v>63.9</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="11">
         <v>79.7</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="11">
         <v>81</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="11">
         <v>78.8</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="11">
         <v>63.1</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="11">
         <v>66.599999999999994</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="12">
         <v>65.7</v>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="19">
         <v>60.420827137582933</v>
       </c>
-      <c r="P8" s="32">
+      <c r="P8" s="26">
         <v>45.27925404347576</v>
       </c>
-      <c r="Q8" s="32">
+      <c r="Q8" s="26">
         <v>39.785591828762811</v>
       </c>
-      <c r="R8" s="32">
+      <c r="R8" s="26">
         <v>44.18457369250482</v>
       </c>
-      <c r="S8" s="32">
+      <c r="S8" s="26">
         <v>37.159844500343013</v>
       </c>
-      <c r="T8" s="32">
+      <c r="T8" s="26">
         <v>38.177163051511151</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="U8" s="26">
+        <v>38.123499531183995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="11">
         <v>89.745095735933276</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="11">
         <v>95.986729601655071</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="11">
         <v>84.030159520297389</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="11">
         <v>100.8</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="11">
         <v>93.4</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="11">
         <v>100.7</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="11">
         <v>98.8</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="11">
         <v>93.2</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="11">
         <v>82</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="11">
         <v>67.5</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="12">
         <v>75.7</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="19">
         <v>69.192377495462793</v>
       </c>
-      <c r="P9" s="32">
+      <c r="P9" s="26">
         <v>66.139521135087193</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="26">
         <v>53.693996785869842</v>
       </c>
-      <c r="R9" s="32">
+      <c r="R9" s="26">
         <v>50.379263611270765</v>
       </c>
-      <c r="S9" s="32">
+      <c r="S9" s="26">
         <v>46.265141318977122</v>
       </c>
-      <c r="T9" s="32">
+      <c r="T9" s="26">
         <v>45.607453560981966</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="U9" s="26">
+        <v>35.920746077253106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="14">
         <v>91.916186358532499</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="14">
         <v>88.339312108260231</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="14">
         <v>87.787489248249415</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="14">
         <v>85.931674123788227</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="14">
         <v>82.549369401254026</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="14">
         <v>86.910817862707191</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="14">
         <v>80.886516217746504</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="14">
         <v>85.344280447787384</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="14">
         <v>76.512240636285668</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="14">
         <v>84.91516258273397</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="15">
         <v>80.2</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="19">
         <v>73.346827375497497</v>
       </c>
-      <c r="P10" s="31">
+      <c r="P10" s="26">
         <v>68.971589575017617</v>
       </c>
-      <c r="Q10" s="31">
+      <c r="Q10" s="26">
         <v>49.132459991853935</v>
       </c>
-      <c r="R10" s="31">
+      <c r="R10" s="26">
         <v>54.819947539591084</v>
       </c>
-      <c r="S10" s="34">
+      <c r="S10" s="28">
         <v>54.165137501740752</v>
       </c>
-      <c r="T10" s="34">
+      <c r="T10" s="28">
         <v>50.172884880431361</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="U10" s="28">
+        <v>44.908357259714307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>75.218009923069715</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>71.207542754783816</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="14">
         <v>71.790057471491053</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="14">
         <v>74.3</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="14">
         <v>72.983332599030334</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="14">
         <v>75.789204457834501</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="14">
         <v>74.3</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="14">
         <v>81.8</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="14">
         <v>66.2</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="14">
         <v>79.5</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="15">
         <v>72.8</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="19">
         <v>64.08958485678572</v>
       </c>
-      <c r="P11" s="31">
+      <c r="P11" s="26">
         <v>67.445157733055012</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="26">
         <v>42.132308166831223</v>
       </c>
-      <c r="R11" s="31">
+      <c r="R11" s="26">
         <v>47.679920417302263</v>
       </c>
-      <c r="S11" s="31">
+      <c r="S11" s="26">
         <v>47.516379220948068</v>
       </c>
-      <c r="T11" s="31">
+      <c r="T11" s="26">
         <v>44.112367891063748</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="U11" s="26">
+        <v>42.913962738120162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="14">
         <v>108.75755289338265</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="14">
         <v>105.62176418872716</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="14">
         <v>103.75710992150292</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="14">
         <v>97.6</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="14">
         <v>92.090531488465757</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="14">
         <v>97.991088993895701</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="14">
         <v>87.5</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="14">
         <v>88.8</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="14">
         <v>86.7</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="14">
         <v>90.3</v>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="15">
         <v>87.5</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O12" s="19">
         <v>82.492292178110617</v>
       </c>
-      <c r="P12" s="32">
+      <c r="P12" s="26">
         <v>70.478671695765442</v>
       </c>
-      <c r="Q12" s="32">
+      <c r="Q12" s="26">
         <v>56.225753650646354</v>
       </c>
-      <c r="R12" s="32">
+      <c r="R12" s="26">
         <v>61.861274529713718</v>
       </c>
-      <c r="S12" s="32">
+      <c r="S12" s="26">
         <v>60.737168699398438</v>
       </c>
-      <c r="T12" s="32">
+      <c r="T12" s="26">
         <v>56.155144351753421</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="U12" s="26">
+        <v>46.874447235292038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="14">
         <v>74.818397450151949</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="14">
         <v>65.710142187525221</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="14">
         <v>68.260472863049017</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="14">
         <v>67.280621149143983</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="14">
         <v>68.345501073360495</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <v>70.114090713433058</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="14">
         <v>69.963198041907731</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="14">
         <v>63.962325106405125</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="14">
         <v>58.459621104565635</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="14">
         <v>60.411218743531137</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="15">
         <v>48.6</v>
       </c>
-      <c r="O13" s="22">
+      <c r="O13" s="19">
         <v>48.933536743329206</v>
       </c>
-      <c r="P13" s="32">
+      <c r="P13" s="26">
         <v>50.313750869839545</v>
       </c>
-      <c r="Q13" s="32">
+      <c r="Q13" s="26">
         <v>28.457427087863305</v>
       </c>
-      <c r="R13" s="32">
+      <c r="R13" s="26">
         <v>36.712395096811576</v>
       </c>
-      <c r="S13" s="35">
+      <c r="S13" s="28">
         <v>38.800251455475774</v>
       </c>
-      <c r="T13" s="35">
+      <c r="T13" s="28">
         <v>37.12775271808399</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="U13" s="28">
+        <v>34.912435590212091</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="14">
         <v>57.509562105762825</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="14">
         <v>56.849190467527748</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="14">
         <v>57.584509766872713</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="14">
         <v>55</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="14">
         <v>53.747679077494382</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="14">
         <v>57.222843359068946</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="14">
         <v>57.9</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="14">
         <v>51.3</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="14">
         <v>48.5</v>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="14">
         <v>53.8</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="15">
         <v>34.799999999999997</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="19">
         <v>34.802404231972361</v>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="26">
         <v>37.584717164899914</v>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="26">
         <v>20.524708126577082</v>
       </c>
-      <c r="R14" s="32">
+      <c r="R14" s="26">
         <v>26.872053459579295</v>
       </c>
-      <c r="S14" s="32">
+      <c r="S14" s="26">
         <v>28.662467801253705</v>
       </c>
-      <c r="T14" s="32">
+      <c r="T14" s="26">
         <v>26.579446704517768</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="U14" s="26">
+        <v>29.995317804050099</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="14">
         <v>92.654431891937648</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="14">
         <v>74.822646944663973</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="14">
         <v>79.185676600172187</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="14">
         <v>79.8</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="14">
         <v>83.206714420085376</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="14">
         <v>83.217008482766019</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="14">
         <v>82.2</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="14">
         <v>76.8</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="14">
         <v>68.5</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="14">
         <v>67.099999999999994</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="15">
         <v>62.4</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="19">
         <v>63.187108177981152</v>
       </c>
-      <c r="P15" s="32">
+      <c r="P15" s="26">
         <v>63.145201372084124</v>
       </c>
-      <c r="Q15" s="32">
+      <c r="Q15" s="26">
         <v>36.325895173845353</v>
       </c>
-      <c r="R15" s="32">
+      <c r="R15" s="26">
         <v>46.638444428499682</v>
       </c>
-      <c r="S15" s="32">
+      <c r="S15" s="26">
         <v>48.983865238282192</v>
       </c>
-      <c r="T15" s="32">
+      <c r="T15" s="26">
         <v>47.691579663423148</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="U15" s="26">
+        <v>39.823606995802081</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="14">
         <v>89.134835007706442</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="14">
         <v>101.24112754534606</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="14">
         <v>97.17194789105902</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="14">
         <v>103.92817834228804</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="14">
         <v>95.240986256460062</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="14">
         <v>105.05659924284207</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="14">
         <v>90.465191293096098</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="14">
         <v>98.190078405510377</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="14">
         <v>84.752208446970101</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="14">
         <v>77.322632262868311</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="15">
         <v>59.5</v>
       </c>
-      <c r="O16" s="22">
+      <c r="O16" s="19">
         <v>67.959770618258759</v>
       </c>
-      <c r="P16" s="32">
+      <c r="P16" s="26">
         <v>55.837827527008514</v>
       </c>
-      <c r="Q16" s="32">
+      <c r="Q16" s="26">
         <v>37.816151622141014</v>
       </c>
-      <c r="R16" s="32">
+      <c r="R16" s="26">
         <v>51.155081745820631</v>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="28">
         <v>52.046737970697684</v>
       </c>
-      <c r="T16" s="35">
+      <c r="T16" s="28">
         <v>49.966474107695483</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="U16" s="28">
+        <v>51.040264388569526</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="14">
         <v>73.136894170160147</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="14">
         <v>93.896008292895445</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="14">
         <v>87.733728135109942</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="14">
         <v>85.5</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="14">
         <v>86.159148255277245</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="14">
         <v>83.765487096307467</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="14">
         <v>76</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="14">
         <v>87</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="14">
         <v>75</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17" s="14">
         <v>63.3</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N17" s="15">
         <v>49</v>
       </c>
-      <c r="O17" s="22">
+      <c r="O17" s="19">
         <v>47.075606276747507</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="26">
         <v>48.742238328353146</v>
       </c>
-      <c r="Q17" s="32">
+      <c r="Q17" s="26">
         <v>29.032279844170926</v>
       </c>
-      <c r="R17" s="32">
+      <c r="R17" s="26">
         <v>43.08338023862634</v>
       </c>
-      <c r="S17" s="32">
+      <c r="S17" s="26">
         <v>42.039438248006412</v>
       </c>
-      <c r="T17" s="32">
+      <c r="T17" s="26">
         <v>44.339536521432947</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="U17" s="26">
+        <v>39.455641509922124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="14">
         <v>104.66452458152487</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="14">
         <v>108.34157407946017</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="14">
         <v>106.39437870275401</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="14">
         <v>121.9</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="14">
         <v>104.08086858854362</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="14">
         <v>125.73592497263394</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="14">
         <v>104.4</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="14">
         <v>109</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="14">
         <v>94.2</v>
       </c>
-      <c r="M18" s="17">
+      <c r="M18" s="14">
         <v>91</v>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="15">
         <v>69.599999999999994</v>
       </c>
-      <c r="O18" s="22">
+      <c r="O18" s="19">
         <v>88.116037807287469</v>
       </c>
-      <c r="P18" s="32">
+      <c r="P18" s="26">
         <v>62.681401338111655</v>
       </c>
-      <c r="Q18" s="32">
+      <c r="Q18" s="26">
         <v>46.928626462141906</v>
       </c>
-      <c r="R18" s="32">
+      <c r="R18" s="26">
         <v>58.934228062068456</v>
       </c>
-      <c r="S18" s="32">
+      <c r="S18" s="26">
         <v>61.864439546842981</v>
       </c>
-      <c r="T18" s="32">
+      <c r="T18" s="26">
         <v>55.468421253968863</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="U18" s="26">
+        <v>62.313531477774838</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="14">
         <v>102.86670812506722</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="14">
         <v>97.93956971327475</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="14">
         <v>99.503115330780261</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="14">
         <v>90.27285526370791</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="14">
         <v>86.981784732809686</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="14">
         <v>89.531840676409175</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="14">
         <v>97.423584429418881</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="14">
         <v>90.681619387581975</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="14">
         <v>91.237868779848242</v>
       </c>
-      <c r="M19" s="17">
+      <c r="M19" s="14">
         <v>83.857442348008377</v>
       </c>
-      <c r="N19" s="18">
+      <c r="N19" s="15">
         <v>84.4</v>
       </c>
-      <c r="O19" s="22">
+      <c r="O19" s="19">
         <v>75.003106303348403</v>
       </c>
-      <c r="P19" s="32">
+      <c r="P19" s="26">
         <v>75.869510346446162</v>
       </c>
-      <c r="Q19" s="32">
+      <c r="Q19" s="26">
         <v>51.38232216208695</v>
       </c>
-      <c r="R19" s="32">
+      <c r="R19" s="26">
         <v>54.51979816984521</v>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="28">
         <v>54.559895023999445</v>
       </c>
-      <c r="T19" s="35">
+      <c r="T19" s="28">
         <v>45.077411133103766</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="U19" s="28">
+        <v>41.347133739830454</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="14">
         <v>85.479057630880433</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="14">
         <v>79.853854477003566</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="14">
         <v>84.498903331437404</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="14">
         <v>83.3</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="14">
         <v>78.306874565821076</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="14">
         <v>79.852654493187359</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="14">
         <v>89.2</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="14">
         <v>82.7</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="14">
         <v>83.8</v>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="14">
         <v>78.400000000000006</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="15">
         <v>73.3</v>
       </c>
-      <c r="O20" s="22">
+      <c r="O20" s="19">
         <v>68.791282379082574</v>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="26">
         <v>70.149044331210945</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="26">
         <v>45.862881450184311</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="26">
         <v>52.474443936678909</v>
       </c>
-      <c r="S20" s="31">
+      <c r="S20" s="26">
         <v>48.115700180781531</v>
       </c>
-      <c r="T20" s="31">
+      <c r="T20" s="26">
         <v>42.341975649266388</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="U20" s="26">
+        <v>38.982485212548049</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="14">
         <v>120.17593458249127</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="14">
         <v>115.9653655032583</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="14">
         <v>114.26834284079327</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="14">
         <v>97.1</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="14">
         <v>95.537625785395988</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="14">
         <v>99.072584784914966</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="14">
         <v>105.5</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="14">
         <v>98.5</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="14">
         <v>98.5</v>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="14">
         <v>89.2</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="15">
         <v>95.3</v>
       </c>
-      <c r="O21" s="22">
+      <c r="O21" s="19">
         <v>81.086922497894577</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="26">
         <v>81.465086808495727</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="26">
         <v>57.0280888993139</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="26">
         <v>56.519551395440942</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="26">
         <v>60.917884338341217</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="26">
         <v>47.772457765110225</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="U21" s="26">
+        <v>43.662463802409043</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="14">
         <v>109.77201551567481</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="14">
         <v>98.863074641621338</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="14">
         <v>98.836800674725893</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="14">
         <v>105.89956034321874</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="14">
         <v>107.889182396938</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="14">
         <v>96.8763689052128</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="14">
         <v>106.45524737382775</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="14">
         <v>101.92599357458536</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="14">
         <v>95.886508888559007</v>
       </c>
-      <c r="M22" s="17">
+      <c r="M22" s="14">
         <v>83.723318128862829</v>
       </c>
-      <c r="N22" s="18">
+      <c r="N22" s="15">
         <v>73.900000000000006</v>
       </c>
-      <c r="O22" s="22">
+      <c r="O22" s="19">
         <v>59.722977266984671</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="26">
         <v>56.142519103528315</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="26">
         <v>44.951834666409091</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="26">
         <v>46.970408642555192</v>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="28">
         <v>44.498872817808376</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="28">
         <v>46.127136558116561</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="U22" s="28">
+        <v>48.779787951392379</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="14">
         <v>86.91149820629461</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="14">
         <v>90.931635942795737</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="14">
         <v>76.560918731024771</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="14">
         <v>87</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="14">
         <v>90.31325798627239</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="14">
         <v>85.593945711404331</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="14">
         <v>89.3</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="14">
         <v>89.6</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="14">
         <v>81</v>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="14">
         <v>67</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="15">
         <v>66</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="19">
         <v>46.443942161810696</v>
       </c>
-      <c r="P23" s="32">
+      <c r="P23" s="26">
         <v>44.202937208965572</v>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="26">
         <v>38.216466887636237</v>
       </c>
-      <c r="R23" s="32">
+      <c r="R23" s="26">
         <v>27.43769048802011</v>
       </c>
-      <c r="S23" s="32">
+      <c r="S23" s="26">
         <v>40.811480640517637</v>
       </c>
-      <c r="T23" s="32">
+      <c r="T23" s="26">
         <v>38.861148383596195</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="U23" s="26">
+        <v>50.038798198603267</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="14">
         <v>132.52712664623539</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="14">
         <v>106.73040083194979</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="14">
         <v>121.0377672917361</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="14">
         <v>124.6</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="14">
         <v>125.30794213671352</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="14">
         <v>108.02482058668365</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="14">
         <v>123.4</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="14">
         <v>114.1</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="14">
         <v>110.5</v>
       </c>
-      <c r="M24" s="17">
+      <c r="M24" s="14">
         <v>100.1</v>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="15">
         <v>81.599999999999994</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="19">
         <v>72.717356724083075</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="26">
         <v>67.817830872763324</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="26">
         <v>51.83682668469686</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="26">
         <v>66.104415920267911</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="26">
         <v>48.122142747774355</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="26">
         <v>53.259250196123595</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="U24" s="26">
+        <v>47.547742901547785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="14">
         <v>158.50619123600544</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="14">
         <v>166.83656847393146</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="14">
         <v>155.18168930613035</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="14">
         <v>154.51760687467808</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="14">
         <v>158.53919203639805</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="14">
         <v>156.78039065049413</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="14">
         <v>144.32061160734867</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="14">
         <v>129.23104050708682</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="14">
         <v>141.65466299843669</v>
       </c>
-      <c r="M25" s="17">
+      <c r="M25" s="14">
         <v>135.21820670758171</v>
       </c>
-      <c r="N25" s="18">
+      <c r="N25" s="15">
         <v>136.19999999999999</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="19">
         <v>124.21760089325016</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="26">
         <v>119.19929216872222</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="26">
         <v>82.176148450436926</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="26">
         <v>88.246666265390886</v>
       </c>
-      <c r="S25" s="35">
+      <c r="S25" s="28">
         <v>86.286397363931727</v>
       </c>
-      <c r="T25" s="35">
+      <c r="T25" s="28">
         <v>77.010722119335071</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="U25" s="28">
+        <v>74.034288036930036</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="14">
         <v>125.92721719062624</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="14">
         <v>125.53429887537868</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="14">
         <v>117.92222504345789</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="14">
         <v>125</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="14">
         <v>112.21888208847271</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="14">
         <v>111.42140523728017</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="14">
         <v>108.3</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="14">
         <v>108.3</v>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="14">
         <v>118.6</v>
       </c>
-      <c r="M26" s="17">
+      <c r="M26" s="14">
         <v>111</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="15">
         <v>108.3</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="19">
         <v>99.197955972182271</v>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="26">
         <v>93.086319420833092</v>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="26">
         <v>66.965035434789911</v>
       </c>
-      <c r="R26" s="31">
+      <c r="R26" s="26">
         <v>71.914698721605745</v>
       </c>
-      <c r="S26" s="31">
+      <c r="S26" s="26">
         <v>68.335423960459067</v>
       </c>
-      <c r="T26" s="31">
+      <c r="T26" s="26">
         <v>59.189709472566221</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="U26" s="26">
+        <v>61.752955023955174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="14">
         <v>191.98836304518144</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="14">
         <v>209.22729644260357</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="14">
         <v>193.79158549851999</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="14">
         <v>185.1</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="14">
         <v>206.42167651164755</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="14">
         <v>203.60269088364058</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="14">
         <v>181.5</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="14">
         <v>150.80000000000001</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="14">
         <v>165.4</v>
       </c>
-      <c r="M27" s="17">
+      <c r="M27" s="14">
         <v>160.19999999999999</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="15">
         <v>165</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="19">
         <v>150.00937558597411</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="26">
         <v>146.10358402344494</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="26">
         <v>96.931980629894966</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="26">
         <v>105.10059183863845</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="26">
         <v>104.46468013142454</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="26">
         <v>95.060584781341987</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="U27" s="26">
+        <v>86.333921344816844</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="14">
         <v>174.38760700216224</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="14">
         <v>123.07557059812528</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="14">
         <v>114.47303689462406</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="14">
         <v>113.11275759525795</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="14">
         <v>114.98415363820473</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="14">
         <v>123.69185126224482</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="14">
         <v>126.39319774790303</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="14">
         <v>133.51149256566563</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="14">
         <v>132.92415200193267</v>
       </c>
-      <c r="M28" s="17">
+      <c r="M28" s="14">
         <v>114.6052000433251</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="15">
         <v>113.1</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="19">
         <v>102.59240461419441</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="26">
         <v>95.331449768398386</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="26">
         <v>56.391242440049062</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="26">
         <v>63.980940123966526</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="28">
         <v>63.925654994479551</v>
       </c>
-      <c r="T28" s="35">
+      <c r="T28" s="28">
         <v>61.976853895626128</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="U28" s="28">
+        <v>57.554242771897933</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="14">
         <v>121.38989063101488</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="14">
         <v>101.46421749813554</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="14">
         <v>90.392820100520368</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="14">
         <v>91.9</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="14">
         <v>90.229385061976174</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="14">
         <v>97.405135638236061</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="14">
         <v>110.2</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="14">
         <v>141.9</v>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="14">
         <v>103.1</v>
       </c>
-      <c r="M29" s="17">
+      <c r="M29" s="14">
         <v>92.2</v>
       </c>
-      <c r="N29" s="18">
+      <c r="N29" s="15">
         <v>91.3</v>
       </c>
-      <c r="O29" s="22">
+      <c r="O29" s="19">
         <v>75.045722301179794</v>
       </c>
-      <c r="P29" s="31">
+      <c r="P29" s="26">
         <v>69.840615031654437</v>
       </c>
-      <c r="Q29" s="31">
+      <c r="Q29" s="26">
         <v>50.844030930786069</v>
       </c>
-      <c r="R29" s="31">
+      <c r="R29" s="26">
         <v>55.546587096180644</v>
       </c>
-      <c r="S29" s="31">
+      <c r="S29" s="26">
         <v>57.785410559676791</v>
       </c>
-      <c r="T29" s="31">
+      <c r="T29" s="26">
         <v>48.390234028455353</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="U29" s="26">
+        <v>46.358023999731095</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="14">
         <v>232.39882637300138</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="14">
         <v>146.69989138074246</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="14">
         <v>142.32790911566585</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="14">
         <v>137.6</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="14">
         <v>143.52973896459932</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="14">
         <v>153.94904845868547</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="14">
         <v>145</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="14">
         <v>123.9</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="14">
         <v>167</v>
       </c>
-      <c r="M30" s="17">
+      <c r="M30" s="14">
         <v>140.19999999999999</v>
       </c>
-      <c r="N30" s="18">
+      <c r="N30" s="15">
         <v>137.80000000000001</v>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="19">
         <v>133.88797197615278</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="26">
         <v>124.20756190394205</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="26">
         <v>61.300998533028128</v>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="26">
         <v>73.505198287622903</v>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="26">
         <v>71.340059495655098</v>
       </c>
-      <c r="T30" s="32">
+      <c r="T30" s="26">
         <v>78.407224173903401</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+      <c r="U30" s="26">
+        <v>71.005160493536351</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="14">
         <v>103.29668569781315</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="14">
         <v>99.531522312648889</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="14">
         <v>99.78418768709534</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="14">
         <v>85.444525142051532</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="14">
         <v>88.724901992206284</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="14">
         <v>98.39240751501066</v>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="14">
         <v>83.705250982585511</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="14">
         <v>103.08200247994384</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="14">
         <v>89.736358242192935</v>
       </c>
-      <c r="M31" s="17">
+      <c r="M31" s="14">
         <v>92.526179888107876</v>
       </c>
-      <c r="N31" s="18">
+      <c r="N31" s="15">
         <v>98.3</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="19">
         <v>84.314452109051217</v>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="26">
         <v>79.086776494887133</v>
       </c>
-      <c r="Q31" s="31">
+      <c r="Q31" s="26">
         <v>54.829571415516767</v>
       </c>
-      <c r="R31" s="31">
+      <c r="R31" s="26">
         <v>43.916363725083563</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="28">
         <v>50.853410128538314</v>
       </c>
-      <c r="T31" s="34">
+      <c r="T31" s="28">
         <v>39.559787476030614</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="U31" s="28">
+        <v>45.478517272228423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="14">
         <v>83.113365090847523</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="14">
         <v>63.749059125332188</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="14">
         <v>82.603421716513978</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="14">
         <v>68</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="14">
         <v>75.035078899385468</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="14">
         <v>78.139534883720927</v>
       </c>
-      <c r="J32" s="17">
+      <c r="J32" s="14">
         <v>64.400000000000006</v>
       </c>
-      <c r="K32" s="17">
+      <c r="K32" s="14">
         <v>92.2</v>
       </c>
-      <c r="L32" s="17">
+      <c r="L32" s="14">
         <v>78.5</v>
       </c>
-      <c r="M32" s="17">
+      <c r="M32" s="14">
         <v>77.599999999999994</v>
       </c>
-      <c r="N32" s="18">
+      <c r="N32" s="15">
         <v>98.3</v>
       </c>
-      <c r="O32" s="22">
+      <c r="O32" s="19">
         <v>83.024189031582139</v>
       </c>
-      <c r="P32" s="31">
+      <c r="P32" s="26">
         <v>76.750352036738676</v>
       </c>
-      <c r="Q32" s="31">
+      <c r="Q32" s="26">
         <v>58.407045187583961</v>
       </c>
-      <c r="R32" s="31">
+      <c r="R32" s="26">
         <v>40.980198843051781</v>
       </c>
-      <c r="S32" s="31">
+      <c r="S32" s="26">
         <v>51.223021582733814</v>
       </c>
-      <c r="T32" s="31">
+      <c r="T32" s="26">
         <v>41.059215262778977</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="U32" s="26">
+        <v>44.530142150589704</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="16">
         <v>125.18464735484841</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="16">
         <v>138.35178023736498</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="16">
         <v>118.37559691096062</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="16">
         <v>104.4</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="16">
         <v>103.6091894008615</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="16">
         <v>120.37972126843063</v>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="16">
         <v>104.5</v>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="16">
         <v>114.8</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="16">
         <v>101.8</v>
       </c>
-      <c r="M33" s="19">
+      <c r="M33" s="16">
         <v>108.5</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="17">
         <v>80.5</v>
       </c>
-      <c r="O33" s="23">
+      <c r="O33" s="20">
         <v>85.689802913453306</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="27">
         <v>81.569917553711434</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="27">
         <v>51.452932817170577</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="27">
         <v>47.015458682814909</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="27">
         <v>50.500891999451071</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="27">
         <v>38.128175110356899</v>
+      </c>
+      <c r="U33" s="27">
+        <v>46.403908052765459</v>
       </c>
     </row>
   </sheetData>
